--- a/data/trans_dic/IP19C01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por revisión o chequeo</t>
+          <t>Menores que en su última visita al dentista fue por revisión o chequeo (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,98; 100,0</t>
+          <t>25,65; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,07; 100,0</t>
+          <t>20,04; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,07; 100,0</t>
+          <t>29,95; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,19; 100,0</t>
+          <t>35,8; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41,19; 100,0</t>
+          <t>46,76; 100,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,66; 100,0</t>
+          <t>18,64; 100,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,33; 92,06</t>
+          <t>49,93; 92,93</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,53; 90,2</t>
+          <t>76,4; 89,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,06; 85,48</t>
+          <t>70,41; 85,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,4; 87,46</t>
+          <t>71,83; 87,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74,26; 90,12</t>
+          <t>74,75; 90,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,32; 90,3</t>
+          <t>77,44; 89,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,34; 87,31</t>
+          <t>73,12; 87,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,86; 86,84</t>
+          <t>72,02; 86,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>74,98; 90,71</t>
+          <t>76,06; 90,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79,3; 88,78</t>
+          <t>78,96; 88,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74,29; 84,77</t>
+          <t>74,88; 84,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74,94; 85,5</t>
+          <t>74,5; 84,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,39; 89,09</t>
+          <t>78,1; 88,91</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63,16; 77,83</t>
+          <t>62,21; 77,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,39; 80,57</t>
+          <t>68,0; 80,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,76; 79,85</t>
+          <t>67,94; 79,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73,06; 87,86</t>
+          <t>73,27; 87,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>73,51; 85,92</t>
+          <t>73,5; 86,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,63; 78,49</t>
+          <t>65,26; 78,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,12; 84,21</t>
+          <t>72,44; 84,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75,8; 87,79</t>
+          <t>76,43; 87,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,78; 79,97</t>
+          <t>70,46; 80,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69,08; 78,06</t>
+          <t>69,23; 78,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,75; 80,78</t>
+          <t>72,64; 80,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>77,38; 86,12</t>
+          <t>77,06; 86,31</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,08; 60,54</t>
+          <t>47,83; 60,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,55; 73,17</t>
+          <t>60,16; 72,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,16; 75,65</t>
+          <t>62,56; 75,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75,79; 85,93</t>
+          <t>76,01; 85,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,01; 65,59</t>
+          <t>53,15; 65,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,17; 80,65</t>
+          <t>69,21; 80,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,12; 76,14</t>
+          <t>62,75; 75,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76,51; 87,03</t>
+          <t>76,13; 86,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,66; 61,28</t>
+          <t>52,36; 61,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66,5; 75,06</t>
+          <t>66,3; 74,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65,09; 74,17</t>
+          <t>64,71; 74,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,98; 85,29</t>
+          <t>77,47; 84,99</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,4; 69,76</t>
+          <t>61,94; 69,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,86; 75,75</t>
+          <t>68,27; 75,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,6; 77,51</t>
+          <t>69,4; 77,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77,96; 84,91</t>
+          <t>78,06; 85,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,59; 75,19</t>
+          <t>67,68; 75,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,97; 79,4</t>
+          <t>72,12; 79,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,19; 79,68</t>
+          <t>72,03; 79,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,51; 85,69</t>
+          <t>78,33; 85,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>65,89; 71,63</t>
+          <t>65,98; 71,78</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,46; 76,69</t>
+          <t>71,36; 76,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,09; 77,36</t>
+          <t>71,97; 77,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,73; 84,54</t>
+          <t>79,27; 84,32</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por revisión o chequeo (tasa de respuesta: 99,77%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4171</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3988</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5030</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2718</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1819</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>8159</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1002; 3906</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>661; 3298</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1736; 5797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1903; 5316</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2711; 5799</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>739; 3967</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5549; 10327</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>70788</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>62049</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55310</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>55323</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>67975</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75349</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>66185</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>65166</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>138763</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>137398</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>121495</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>120489</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>64431; 75476</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>55612; 67870</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>49406; 60188</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>49483; 59652</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>62274; 72352</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>67771; 81202</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>59608; 71842</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>58664; 70148</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>130092; 145905</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>128544; 145870</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>112904; 128698</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>111944; 127427</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>69875</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>94226</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>111270</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>99990</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84978</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96269</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>119023</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>135743</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>154853</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>190495</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>230293</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>235733</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>61710; 76867</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>85565; 101432</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>101791; 119298</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>89315; 106865</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>77706; 91181</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>86203; 103453</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>109086; 126537</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>125955; 143825</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>144380; 163939</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>178554; 201243</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>218221; 241900</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>220916; 247442</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>88418</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98469</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>101452</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>160382</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>103374</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>106845</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95481</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>194374</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>191791</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>205313</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>196933</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>354756</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>78205; 98439</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>88995; 107383</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>91263; 110126</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>150298; 169673</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>92322; 114052</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>98246; 114375</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>85828; 103876</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>180584; 206054</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>176568; 206475</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>192186; 217291</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>182902; 210565</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>336940; 369641</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>232218</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>256792</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>268568</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>319866</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>258220</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>279132</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>281974</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>399272</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>490437</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>535924</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>550541</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>719137</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>217367; 245325</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>243057; 269024</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>253328; 282120</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>305727; 332886</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>244823; 271292</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>264985; 292453</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>267518; 294469</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>379470; 414420</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>470225; 511548</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>516222; 555101</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>529969; 569772</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>694445; 738683</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Edad-trans_dic.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,65; 100,0</t>
+          <t>28,09; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,95; 100,0</t>
+          <t>35,8; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,8; 100,0</t>
+          <t>36,47; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,76; 100,0</t>
+          <t>45,4; 100,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,64; 100,0</t>
+          <t>17,45; 100,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,93; 92,93</t>
+          <t>48,57; 93,04</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,4; 89,5</t>
+          <t>76,6; 90,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,41; 85,93</t>
+          <t>69,76; 85,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,83; 87,5</t>
+          <t>71,85; 87,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74,75; 90,11</t>
+          <t>75,57; 90,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,44; 89,97</t>
+          <t>77,89; 90,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,12; 87,62</t>
+          <t>73,2; 86,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,02; 86,81</t>
+          <t>72,32; 86,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>76,06; 90,95</t>
+          <t>75,45; 91,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78,96; 88,56</t>
+          <t>79,3; 88,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74,88; 84,98</t>
+          <t>74,75; 84,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74,5; 84,92</t>
+          <t>74,08; 84,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,1; 88,91</t>
+          <t>78,27; 88,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,21; 77,49</t>
+          <t>62,6; 77,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,0; 80,62</t>
+          <t>67,88; 80,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,94; 79,63</t>
+          <t>68,21; 79,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73,27; 87,66</t>
+          <t>72,61; 87,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>73,5; 86,25</t>
+          <t>73,47; 86,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,26; 78,32</t>
+          <t>66,09; 78,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,44; 84,03</t>
+          <t>73,67; 84,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76,43; 87,28</t>
+          <t>76,43; 87,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,46; 80,0</t>
+          <t>70,59; 80,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69,23; 78,03</t>
+          <t>69,29; 78,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,64; 80,52</t>
+          <t>72,47; 80,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>77,06; 86,31</t>
+          <t>77,39; 86,2</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,83; 60,21</t>
+          <t>47,72; 60,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,16; 72,6</t>
+          <t>59,24; 71,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,56; 75,49</t>
+          <t>62,93; 75,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76,01; 85,81</t>
+          <t>75,67; 85,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,15; 65,66</t>
+          <t>53,52; 64,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,21; 80,57</t>
+          <t>69,54; 81,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,75; 75,95</t>
+          <t>63,46; 76,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76,13; 86,87</t>
+          <t>75,69; 86,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,36; 61,23</t>
+          <t>52,59; 61,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66,3; 74,96</t>
+          <t>65,88; 74,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64,71; 74,5</t>
+          <t>64,71; 73,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,47; 84,99</t>
+          <t>77,82; 85,41</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,94; 69,91</t>
+          <t>61,72; 69,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,27; 75,56</t>
+          <t>68,27; 76,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,4; 77,29</t>
+          <t>69,72; 77,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78,06; 85,0</t>
+          <t>77,71; 84,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,68; 75,0</t>
+          <t>67,62; 74,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,12; 79,6</t>
+          <t>72,1; 79,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,03; 79,29</t>
+          <t>72,19; 79,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,33; 85,55</t>
+          <t>78,68; 85,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>65,98; 71,78</t>
+          <t>66,07; 71,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,36; 76,73</t>
+          <t>71,43; 76,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71,97; 77,37</t>
+          <t>72,01; 77,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,27; 84,32</t>
+          <t>79,53; 84,44</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1002; 3906</t>
+          <t>1097; 3906</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1736; 5797</t>
+          <t>2075; 5797</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1680,17 +1680,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1903; 5316</t>
+          <t>1939; 5316</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2711; 5799</t>
+          <t>2633; 5799</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>739; 3967</t>
+          <t>692; 3967</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5549; 10327</t>
+          <t>5398; 10339</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64431; 75476</t>
+          <t>64600; 76138</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55612; 67870</t>
+          <t>55098; 67397</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49406; 60188</t>
+          <t>49422; 60158</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49483; 59652</t>
+          <t>50024; 59683</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62274; 72352</t>
+          <t>62637; 72886</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67771; 81202</t>
+          <t>67839; 80548</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59608; 71842</t>
+          <t>59850; 71772</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58664; 70148</t>
+          <t>58199; 70243</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>130092; 145905</t>
+          <t>130653; 145560</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128544; 145870</t>
+          <t>128319; 145547</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>112904; 128698</t>
+          <t>112270; 128648</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>111944; 127427</t>
+          <t>112179; 127215</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>61710; 76867</t>
+          <t>62092; 76654</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85565; 101432</t>
+          <t>85409; 101782</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101791; 119298</t>
+          <t>102195; 119413</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89315; 106865</t>
+          <t>88516; 107254</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>77706; 91181</t>
+          <t>77672; 91205</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86203; 103453</t>
+          <t>87296; 103869</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>109086; 126537</t>
+          <t>110932; 126977</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>125955; 143825</t>
+          <t>125941; 144446</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>144380; 163939</t>
+          <t>144642; 164702</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>178554; 201243</t>
+          <t>178715; 201362</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>218221; 241900</t>
+          <t>217695; 242829</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>220916; 247442</t>
+          <t>221879; 247117</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78205; 98439</t>
+          <t>78028; 98472</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88995; 107383</t>
+          <t>87622; 106473</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91263; 110126</t>
+          <t>91809; 110726</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>150298; 169673</t>
+          <t>149628; 169036</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92322; 114052</t>
+          <t>92968; 112563</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>98246; 114375</t>
+          <t>98719; 115056</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85828; 103876</t>
+          <t>86788; 104704</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>180584; 206054</t>
+          <t>179550; 206090</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>176568; 206475</t>
+          <t>177345; 206609</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>192186; 217291</t>
+          <t>190982; 217367</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182902; 210565</t>
+          <t>182902; 208515</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>336940; 369641</t>
+          <t>338488; 371500</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>217367; 245325</t>
+          <t>216587; 244928</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>243057; 269024</t>
+          <t>243040; 270963</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>253328; 282120</t>
+          <t>254511; 283010</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>305727; 332886</t>
+          <t>304341; 332207</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>244823; 271292</t>
+          <t>244598; 271064</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>264985; 292453</t>
+          <t>264906; 292529</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>267518; 294469</t>
+          <t>268115; 294193</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>379470; 414420</t>
+          <t>381145; 414784</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>470225; 511548</t>
+          <t>470844; 509320</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>516222; 555101</t>
+          <t>516752; 553917</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>529969; 569772</t>
+          <t>530285; 568634</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>694445; 738683</t>
+          <t>696742; 739765</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>77,21%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>80,33%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>62,14%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71,95%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>76,05%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>86,75%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>68,52%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>75,02%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>86,75%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>68,52%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,09; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,04; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,8; 100,0</t>
+          <t>38,49; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>22,98; 100,0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,07; 100,0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>40,18; 100,0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>41,19; 100,0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17,66; 100,0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>36,47; 100,0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>45,4; 100,0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17,45; 100,0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,57; 93,04</t>
+          <t>52,12; 93,14</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>84,53%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81,3%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>79,97%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>84,71%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>83,94%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>78,56%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>80,41%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>83,57%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>84,53%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>81,3%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>79,97%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,6; 90,28</t>
+          <t>77,32; 90,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69,76; 85,33</t>
+          <t>74,34; 87,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,85; 87,46</t>
+          <t>71,86; 86,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,57; 90,16</t>
+          <t>75,44; 90,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,89; 90,63</t>
+          <t>76,53; 90,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,2; 86,91</t>
+          <t>70,06; 85,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,32; 86,72</t>
+          <t>71,4; 87,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,45; 91,07</t>
+          <t>73,05; 89,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79,3; 88,35</t>
+          <t>79,3; 88,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74,75; 84,79</t>
+          <t>74,29; 84,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74,08; 84,89</t>
+          <t>74,94; 85,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,27; 88,76</t>
+          <t>78,01; 88,81</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>80,38%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72,88%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>79,04%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82,27%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>70,44%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>74,89%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>74,27%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>82,02%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>80,38%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>79,04%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,6; 77,28</t>
+          <t>73,51; 85,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67,88; 80,89</t>
+          <t>66,63; 78,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68,21; 79,7</t>
+          <t>73,12; 84,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72,61; 87,98</t>
+          <t>75,53; 87,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>73,47; 86,27</t>
+          <t>63,16; 77,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,09; 78,64</t>
+          <t>68,39; 80,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,67; 84,32</t>
+          <t>67,76; 79,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76,43; 87,66</t>
+          <t>76,94; 88,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,59; 80,38</t>
+          <t>70,78; 79,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69,29; 78,08</t>
+          <t>69,08; 78,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,47; 80,83</t>
+          <t>72,75; 80,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>77,39; 86,2</t>
+          <t>78,57; 86,64</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>59,51%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>75,26%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>69,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>82,23%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>54,08%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>66,57%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>69,54%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>81,11%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>59,51%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>75,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>69,81%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,72; 60,23</t>
+          <t>54,01; 65,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,24; 71,98</t>
+          <t>69,17; 80,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,93; 75,9</t>
+          <t>63,12; 76,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75,67; 85,49</t>
+          <t>76,35; 87,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,52; 64,8</t>
+          <t>48,08; 60,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,54; 81,05</t>
+          <t>60,55; 73,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,46; 76,56</t>
+          <t>63,16; 75,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75,69; 86,88</t>
+          <t>75,38; 85,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,59; 61,27</t>
+          <t>52,66; 61,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65,88; 74,98</t>
+          <t>66,5; 75,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64,71; 73,77</t>
+          <t>65,09; 74,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,82; 85,41</t>
+          <t>77,87; 85,32</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>71,38%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75,98%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75,92%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82,56%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>66,17%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>72,13%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>73,58%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>81,67%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>75,98%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>75,92%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,72; 69,79</t>
+          <t>67,59; 75,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,27; 76,11</t>
+          <t>71,97; 79,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,72; 77,53</t>
+          <t>72,19; 79,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77,71; 84,83</t>
+          <t>78,56; 85,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,62; 74,94</t>
+          <t>61,4; 69,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,1; 79,62</t>
+          <t>67,86; 75,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,19; 79,21</t>
+          <t>69,6; 77,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,68; 85,62</t>
+          <t>78,44; 85,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66,07; 71,47</t>
+          <t>65,89; 71,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,43; 76,57</t>
+          <t>71,46; 76,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,01; 77,22</t>
+          <t>72,09; 77,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,53; 84,44</t>
+          <t>79,84; 84,58</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3610</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3138</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2049</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4171</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>8228</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1097; 3906</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>661; 3298</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1660,47 +1660,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2075; 5797</t>
+          <t>1800; 4676</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>898; 3906</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>662; 3298</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2440; 6072</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2389; 5799</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>700; 3967</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1939; 5316</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2633; 5799</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>692; 3967</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5398; 10339</t>
+          <t>5602; 10011</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>86</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>67975</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>75349</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>66185</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>57238</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>70788</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>62049</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>55310</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>55323</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>67975</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75349</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>66185</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>65166</t>
+          <t>52397</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>120489</t>
+          <t>109636</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64600; 76138</t>
+          <t>62182; 72618</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55098; 67397</t>
+          <t>68894; 80914</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49422; 60158</t>
+          <t>59476; 71872</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50024; 59683</t>
+          <t>50976; 61282</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62637; 72886</t>
+          <t>64545; 76069</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67839; 80548</t>
+          <t>55335; 67512</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59850; 71772</t>
+          <t>49111; 60156</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58199; 70243</t>
+          <t>46351; 56898</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>130653; 145560</t>
+          <t>130656; 146275</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128319; 145547</t>
+          <t>127523; 145522</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>112270; 128648</t>
+          <t>113572; 129578</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>112179; 127215</t>
+          <t>102213; 116364</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>136</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>84978</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>96269</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>119023</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>127756</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>69875</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>94226</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>111270</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>99990</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>84978</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96269</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>119023</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>135743</t>
+          <t>101825</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>235733</t>
+          <t>229582</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>62092; 76654</t>
+          <t>77715; 90833</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85409; 101782</t>
+          <t>88011; 103671</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102195; 119413</t>
+          <t>110105; 126811</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88516; 107254</t>
+          <t>117301; 135931</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>77672; 91205</t>
+          <t>62646; 77199</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87296; 103869</t>
+          <t>86046; 101371</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>110932; 126977</t>
+          <t>101523; 119630</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>125941; 144446</t>
+          <t>93738; 108363</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>144642; 164702</t>
+          <t>145035; 163860</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>178715; 201362</t>
+          <t>178156; 201323</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>217695; 242829</t>
+          <t>218558; 242670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>221879; 247117</t>
+          <t>217737; 240120</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>139</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>229</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>103374</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>106845</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>95481</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>192053</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>88418</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>98469</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>101452</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>160382</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>103374</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>106845</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95481</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>194374</t>
+          <t>165569</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>354756</t>
+          <t>357622</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78028; 98472</t>
+          <t>93823; 113931</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87622; 106473</t>
+          <t>98189; 114494</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91809; 110726</t>
+          <t>86323; 104132</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>149628; 169036</t>
+          <t>178322; 203472</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92968; 112563</t>
+          <t>78614; 98978</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>98719; 115056</t>
+          <t>89572; 108234</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86788; 104704</t>
+          <t>92138; 110355</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>179550; 206090</t>
+          <t>154456; 175509</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177345; 206609</t>
+          <t>177551; 206646</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>190982; 217367</t>
+          <t>192765; 217585</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182902; 208515</t>
+          <t>183976; 209650</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>338488; 371500</t>
+          <t>341421; 374088</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>363</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>386</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>460</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>258220</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>279132</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>281974</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>380658</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>232218</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>256792</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>268568</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>319866</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>258220</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>279132</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>281974</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>399272</t>
+          <t>324410</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>719137</t>
+          <t>705067</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>216587; 244928</t>
+          <t>244477; 272001</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>243040; 270963</t>
+          <t>264423; 291726</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>254511; 283010</t>
+          <t>268126; 295931</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>304341; 332207</t>
+          <t>362215; 394644</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>244598; 271064</t>
+          <t>215484; 244818</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>264906; 292529</t>
+          <t>241589; 269703</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>268115; 294193</t>
+          <t>254062; 282940</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>381145; 414784</t>
+          <t>310839; 337298</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>470844; 509320</t>
+          <t>469582; 510472</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>516752; 553917</t>
+          <t>516958; 554768</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>530285; 568634</t>
+          <t>530895; 569710</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>696742; 739765</t>
+          <t>684521; 725196</t>
         </is>
       </c>
     </row>
